--- a/Data/Fiscal Data/ngdebt.xlsx
+++ b/Data/Fiscal Data/ngdebt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AJ\GitHub Repositories\PH-Econ-Data\Data\Fiscal Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E2643B-5041-4838-B903-678F4CA1EEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77986656-7329-497B-BD2C-8096EB64BA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13830" yWindow="735" windowWidth="14715" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="825" yWindow="720" windowWidth="14715" windowHeight="13245" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ngdebt" sheetId="1" r:id="rId1"/>
@@ -1664,17 +1664,20 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1683,6 +1686,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -17198,9 +17202,15 @@
       <c r="RJ13" s="2">
         <v>81704</v>
       </c>
-      <c r="RK13" s="2"/>
-      <c r="RL13" s="2"/>
-      <c r="RM13" s="2"/>
+      <c r="RK13" s="2">
+        <v>57367</v>
+      </c>
+      <c r="RL13" s="2">
+        <v>77289</v>
+      </c>
+      <c r="RM13" s="2">
+        <v>63634</v>
+      </c>
     </row>
     <row r="14" spans="1:481" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -18637,9 +18647,15 @@
       <c r="RJ14" s="2">
         <v>246188</v>
       </c>
-      <c r="RK14" s="2"/>
-      <c r="RL14" s="2"/>
-      <c r="RM14" s="2"/>
+      <c r="RK14" s="2">
+        <v>8417</v>
+      </c>
+      <c r="RL14" s="2">
+        <v>12680</v>
+      </c>
+      <c r="RM14" s="2">
+        <v>15008</v>
+      </c>
     </row>
     <row r="19" spans="421:433" x14ac:dyDescent="0.25">
       <c r="PE19" s="2"/>
@@ -19952,7 +19968,9 @@
       <c r="AX9" s="2">
         <v>763313</v>
       </c>
-      <c r="AY9" s="2"/>
+      <c r="AY9" s="2">
+        <v>864139</v>
+      </c>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -20090,7 +20108,9 @@
       <c r="AX10" s="2">
         <v>1257329</v>
       </c>
-      <c r="AY10" s="2"/>
+      <c r="AY10" s="2">
+        <v>1239032</v>
+      </c>
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
@@ -20212,6 +20232,9 @@
       </c>
       <c r="AX11">
         <v>57.847000000000001</v>
+      </c>
+      <c r="AY11">
+        <v>58.79</v>
       </c>
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.25">

--- a/Data/Fiscal Data/ngdebt.xlsx
+++ b/Data/Fiscal Data/ngdebt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AJ\GitHub Repositories\PH-Econ-Data\Data\Fiscal Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77986656-7329-497B-BD2C-8096EB64BA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0846D7-A126-4F88-9A0B-A9B961C73E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="720" windowWidth="14715" windowHeight="13245" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ngdebt" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="543">
   <si>
     <t>Particulars</t>
   </si>
@@ -1511,9 +1511,6 @@
     <t xml:space="preserve">    External</t>
   </si>
   <si>
-    <t>1993 - 2023</t>
-  </si>
-  <si>
     <t>January 2024</t>
   </si>
   <si>
@@ -1556,18 +1553,6 @@
     <t>Debt Service - Amortization</t>
   </si>
   <si>
-    <t>2009 - 2024</t>
-  </si>
-  <si>
-    <t>1993 - 2024</t>
-  </si>
-  <si>
-    <t>1995 - 2008; 2009 - 2024</t>
-  </si>
-  <si>
-    <t>1986 - 2024</t>
-  </si>
-  <si>
     <t>January 2025</t>
   </si>
   <si>
@@ -1632,6 +1617,54 @@
   </si>
   <si>
     <t>CBP Reports 1965-1986; PSY 1977</t>
+  </si>
+  <si>
+    <t>January 2026</t>
+  </si>
+  <si>
+    <t>February 2026</t>
+  </si>
+  <si>
+    <t>March 2026</t>
+  </si>
+  <si>
+    <t>April 2026</t>
+  </si>
+  <si>
+    <t>May 2026</t>
+  </si>
+  <si>
+    <t>June 2026</t>
+  </si>
+  <si>
+    <t>July 2026</t>
+  </si>
+  <si>
+    <t>August 2026</t>
+  </si>
+  <si>
+    <t>September 2026</t>
+  </si>
+  <si>
+    <t>October 2026</t>
+  </si>
+  <si>
+    <t>November 2026</t>
+  </si>
+  <si>
+    <t>December 2026</t>
+  </si>
+  <si>
+    <t>2009 - 2025</t>
+  </si>
+  <si>
+    <t>1993 - 2025</t>
+  </si>
+  <si>
+    <t>1995 - 2008; 2009 - 2025</t>
+  </si>
+  <si>
+    <t>1986 - 2025</t>
   </si>
 </sst>
 </file>
@@ -1747,7 +1780,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1756,17 +1789,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1996,14 +2030,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:RM19"/>
+  <dimension ref="A1:RY19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="481" width="10.7109375" customWidth="1"/>
+    <col min="2" max="493" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3376,79 +3410,115 @@
         <v>456</v>
       </c>
       <c r="QP1" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="QQ1" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="QQ1" s="1" t="s">
+      <c r="QR1" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="QR1" s="1" t="s">
+      <c r="QS1" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="QS1" s="1" t="s">
+      <c r="QT1" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="QT1" s="1" t="s">
+      <c r="QU1" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="QU1" s="1" t="s">
+      <c r="QV1" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="QV1" s="1" t="s">
+      <c r="QW1" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="QW1" s="1" t="s">
+      <c r="QX1" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="QX1" s="1" t="s">
+      <c r="QY1" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="QY1" s="1" t="s">
+      <c r="QZ1" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="QZ1" s="1" t="s">
+      <c r="RA1" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="RA1" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="RB1" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="RC1" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="RD1" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="RE1" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="RF1" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="RG1" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="RC1" s="1" t="s">
+      <c r="RH1" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="RD1" s="1" t="s">
+      <c r="RI1" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="RE1" s="1" t="s">
+      <c r="RJ1" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="RF1" s="1" t="s">
+      <c r="RK1" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="RG1" s="1" t="s">
+      <c r="RL1" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="RH1" s="1" t="s">
+      <c r="RM1" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="RI1" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="RJ1" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="RK1" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="RL1" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="RM1" s="1" t="s">
-        <v>521</v>
+      <c r="RN1" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="RO1" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="RP1" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="RQ1" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="RR1" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="RS1" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="RT1" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="RU1" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="RV1" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="RW1" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="RX1" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="RY1" s="1" t="s">
+        <v>538</v>
       </c>
     </row>
-    <row r="2" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>457</v>
       </c>
@@ -4340,8 +4410,26 @@
       <c r="RM2" s="2">
         <v>18052386</v>
       </c>
+      <c r="RN2" s="2">
+        <v>18479047</v>
+      </c>
+      <c r="RO2" s="2">
+        <v>18539680</v>
+      </c>
+      <c r="RP2" s="2">
+        <v>18869540</v>
+      </c>
+      <c r="RQ2" s="2"/>
+      <c r="RR2" s="2"/>
+      <c r="RS2" s="2"/>
+      <c r="RT2" s="2"/>
+      <c r="RU2" s="2"/>
+      <c r="RV2" s="2"/>
+      <c r="RW2" s="2"/>
+      <c r="RX2" s="2"/>
+      <c r="RY2" s="2"/>
     </row>
-    <row r="3" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>458</v>
       </c>
@@ -5617,8 +5705,26 @@
       <c r="RM3" s="2">
         <v>17707814</v>
       </c>
+      <c r="RN3" s="2">
+        <v>18133963</v>
+      </c>
+      <c r="RO3" s="2">
+        <v>18159698</v>
+      </c>
+      <c r="RP3" s="2">
+        <v>18488134</v>
+      </c>
+      <c r="RQ3" s="2"/>
+      <c r="RR3" s="2"/>
+      <c r="RS3" s="2"/>
+      <c r="RT3" s="2"/>
+      <c r="RU3" s="2"/>
+      <c r="RV3" s="2"/>
+      <c r="RW3" s="2"/>
+      <c r="RX3" s="2"/>
+      <c r="RY3" s="2"/>
     </row>
-    <row r="4" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>459</v>
       </c>
@@ -6894,8 +7000,26 @@
       <c r="RM4" s="2">
         <v>12116253</v>
       </c>
+      <c r="RN4" s="2">
+        <v>12324775</v>
+      </c>
+      <c r="RO4" s="2">
+        <v>12479162</v>
+      </c>
+      <c r="RP4" s="2">
+        <v>12534566</v>
+      </c>
+      <c r="RQ4" s="2"/>
+      <c r="RR4" s="2"/>
+      <c r="RS4" s="2"/>
+      <c r="RT4" s="2"/>
+      <c r="RU4" s="2"/>
+      <c r="RV4" s="2"/>
+      <c r="RW4" s="2"/>
+      <c r="RX4" s="2"/>
+      <c r="RY4" s="2"/>
     </row>
-    <row r="5" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>460</v>
       </c>
@@ -8123,8 +8247,26 @@
       <c r="RM5" s="2">
         <v>156</v>
       </c>
+      <c r="RN5" s="2">
+        <v>156</v>
+      </c>
+      <c r="RO5" s="2">
+        <v>156</v>
+      </c>
+      <c r="RP5" s="2">
+        <v>156</v>
+      </c>
+      <c r="RQ5" s="2"/>
+      <c r="RR5" s="2"/>
+      <c r="RS5" s="2"/>
+      <c r="RT5" s="2"/>
+      <c r="RU5" s="2"/>
+      <c r="RV5" s="2"/>
+      <c r="RW5" s="2"/>
+      <c r="RX5" s="2"/>
+      <c r="RY5" s="2"/>
     </row>
-    <row r="6" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>461</v>
       </c>
@@ -9352,8 +9494,26 @@
       <c r="RM6" s="2">
         <v>12116097</v>
       </c>
+      <c r="RN6" s="2">
+        <v>12324619</v>
+      </c>
+      <c r="RO6" s="2">
+        <v>12479006</v>
+      </c>
+      <c r="RP6" s="2">
+        <v>12534410</v>
+      </c>
+      <c r="RQ6" s="2"/>
+      <c r="RR6" s="2"/>
+      <c r="RS6" s="2"/>
+      <c r="RT6" s="2"/>
+      <c r="RU6" s="2"/>
+      <c r="RV6" s="2"/>
+      <c r="RW6" s="2"/>
+      <c r="RX6" s="2"/>
+      <c r="RY6" s="2"/>
     </row>
-    <row r="7" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>462</v>
       </c>
@@ -10629,8 +10789,26 @@
       <c r="RM7" s="2">
         <v>5591561</v>
       </c>
+      <c r="RN7" s="2">
+        <v>5809188</v>
+      </c>
+      <c r="RO7" s="2">
+        <v>5680536</v>
+      </c>
+      <c r="RP7" s="2">
+        <v>5953568</v>
+      </c>
+      <c r="RQ7" s="2"/>
+      <c r="RR7" s="2"/>
+      <c r="RS7" s="2"/>
+      <c r="RT7" s="2"/>
+      <c r="RU7" s="2"/>
+      <c r="RV7" s="2"/>
+      <c r="RW7" s="2"/>
+      <c r="RX7" s="2"/>
+      <c r="RY7" s="2"/>
     </row>
-    <row r="8" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>463</v>
       </c>
@@ -11858,8 +12036,26 @@
       <c r="RM8" s="2">
         <v>2769078</v>
       </c>
+      <c r="RN8" s="2">
+        <v>2813820</v>
+      </c>
+      <c r="RO8" s="2">
+        <v>2753189</v>
+      </c>
+      <c r="RP8" s="2">
+        <v>2944109</v>
+      </c>
+      <c r="RQ8" s="2"/>
+      <c r="RR8" s="2"/>
+      <c r="RS8" s="2"/>
+      <c r="RT8" s="2"/>
+      <c r="RU8" s="2"/>
+      <c r="RV8" s="2"/>
+      <c r="RW8" s="2"/>
+      <c r="RX8" s="2"/>
+      <c r="RY8" s="2"/>
     </row>
-    <row r="9" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>464</v>
       </c>
@@ -13087,8 +13283,26 @@
       <c r="RM9" s="2">
         <v>2822483</v>
       </c>
+      <c r="RN9" s="2">
+        <v>2995368</v>
+      </c>
+      <c r="RO9" s="2">
+        <v>2927347</v>
+      </c>
+      <c r="RP9" s="2">
+        <v>3009459</v>
+      </c>
+      <c r="RQ9" s="2"/>
+      <c r="RR9" s="2"/>
+      <c r="RS9" s="2"/>
+      <c r="RT9" s="2"/>
+      <c r="RU9" s="2"/>
+      <c r="RV9" s="2"/>
+      <c r="RW9" s="2"/>
+      <c r="RX9" s="2"/>
+      <c r="RY9" s="2"/>
     </row>
-    <row r="10" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>465</v>
       </c>
@@ -13980,8 +14194,26 @@
       <c r="RM10" s="2">
         <v>344572</v>
       </c>
+      <c r="RN10" s="2">
+        <v>345084</v>
+      </c>
+      <c r="RO10" s="2">
+        <v>379982</v>
+      </c>
+      <c r="RP10" s="2">
+        <v>381406</v>
+      </c>
+      <c r="RQ10" s="2"/>
+      <c r="RR10" s="2"/>
+      <c r="RS10" s="2"/>
+      <c r="RT10" s="2"/>
+      <c r="RU10" s="2"/>
+      <c r="RV10" s="2"/>
+      <c r="RW10" s="2"/>
+      <c r="RX10" s="2"/>
+      <c r="RY10" s="2"/>
     </row>
-    <row r="11" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>466</v>
       </c>
@@ -14873,8 +15105,26 @@
       <c r="RM11" s="2">
         <v>256732</v>
       </c>
+      <c r="RN11" s="2">
+        <v>256731</v>
+      </c>
+      <c r="RO11" s="2">
+        <v>294030</v>
+      </c>
+      <c r="RP11" s="2">
+        <v>293268</v>
+      </c>
+      <c r="RQ11" s="2"/>
+      <c r="RR11" s="2"/>
+      <c r="RS11" s="2"/>
+      <c r="RT11" s="2"/>
+      <c r="RU11" s="2"/>
+      <c r="RV11" s="2"/>
+      <c r="RW11" s="2"/>
+      <c r="RX11" s="2"/>
+      <c r="RY11" s="2"/>
     </row>
-    <row r="12" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>467</v>
       </c>
@@ -15766,10 +16016,28 @@
       <c r="RM12" s="2">
         <v>87840</v>
       </c>
+      <c r="RN12" s="2">
+        <v>88353</v>
+      </c>
+      <c r="RO12" s="2">
+        <v>85952</v>
+      </c>
+      <c r="RP12" s="2">
+        <v>88138</v>
+      </c>
+      <c r="RQ12" s="2"/>
+      <c r="RR12" s="2"/>
+      <c r="RS12" s="2"/>
+      <c r="RT12" s="2"/>
+      <c r="RU12" s="2"/>
+      <c r="RV12" s="2"/>
+      <c r="RW12" s="2"/>
+      <c r="RX12" s="2"/>
+      <c r="RY12" s="2"/>
     </row>
-    <row r="13" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B13" s="2">
         <v>915</v>
@@ -17211,10 +17479,28 @@
       <c r="RM13" s="2">
         <v>63634</v>
       </c>
+      <c r="RN13" s="2">
+        <v>127817</v>
+      </c>
+      <c r="RO13" s="2">
+        <v>48931</v>
+      </c>
+      <c r="RP13" s="2">
+        <v>96383</v>
+      </c>
+      <c r="RQ13" s="2"/>
+      <c r="RR13" s="2"/>
+      <c r="RS13" s="2"/>
+      <c r="RT13" s="2"/>
+      <c r="RU13" s="2"/>
+      <c r="RV13" s="2"/>
+      <c r="RW13" s="2"/>
+      <c r="RX13" s="2"/>
+      <c r="RY13" s="2"/>
     </row>
-    <row r="14" spans="1:481" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:493" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B14" s="2">
         <v>1169</v>
@@ -18656,6 +18942,24 @@
       <c r="RM14" s="2">
         <v>15008</v>
       </c>
+      <c r="RN14" s="2">
+        <v>9852</v>
+      </c>
+      <c r="RO14" s="2">
+        <v>381713</v>
+      </c>
+      <c r="RP14" s="2">
+        <v>72709</v>
+      </c>
+      <c r="RQ14" s="2"/>
+      <c r="RR14" s="2"/>
+      <c r="RS14" s="2"/>
+      <c r="RT14" s="2"/>
+      <c r="RU14" s="2"/>
+      <c r="RV14" s="2"/>
+      <c r="RW14" s="2"/>
+      <c r="RX14" s="2"/>
+      <c r="RY14" s="2"/>
     </row>
     <row r="19" spans="421:433" x14ac:dyDescent="0.25">
       <c r="PE19" s="2"/>
@@ -18832,7 +19136,7 @@
       </c>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>457</v>
       </c>
       <c r="L2" s="2">
@@ -19828,27 +20132,27 @@
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>504</v>
-      </c>
-      <c r="E9" s="11">
+        <v>503</v>
+      </c>
+      <c r="E9" s="10">
         <v>1841</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <v>2296</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <v>2429</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="10">
         <v>3560</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="10">
         <v>4997</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <v>10409</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="10">
         <v>14652</v>
       </c>
       <c r="L9" s="2">
@@ -19974,21 +20278,21 @@
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>505</v>
-      </c>
-      <c r="G10" s="9">
+        <v>504</v>
+      </c>
+      <c r="G10" s="8">
         <v>1468</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>1332</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>3451</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>4473</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="8">
         <v>6951</v>
       </c>
       <c r="L10" s="2">
@@ -20113,8 +20417,8 @@
       </c>
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>523</v>
+      <c r="A11" s="9" t="s">
+        <v>518</v>
       </c>
       <c r="L11">
         <v>20.53</v>
@@ -20330,8 +20634,8 @@
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>524</v>
+      <c r="A2" s="9" t="s">
+        <v>519</v>
       </c>
       <c r="B2" s="2">
         <f t="shared" ref="B2" si="0">B3+B5</f>
@@ -20426,8 +20730,8 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>525</v>
+      <c r="A3" s="9" t="s">
+        <v>520</v>
       </c>
       <c r="B3" s="2">
         <v>3138.9</v>
@@ -20450,7 +20754,7 @@
       <c r="H3" s="2">
         <v>6956.7</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>9701.4</v>
       </c>
       <c r="J3" s="2">
@@ -20499,8 +20803,8 @@
       <c r="Y3" s="2"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>526</v>
+      <c r="A4" s="9" t="s">
+        <v>521</v>
       </c>
       <c r="B4" s="2">
         <v>2938.5</v>
@@ -20523,7 +20827,7 @@
       <c r="H4" s="2">
         <v>4130.5</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>5607.8</v>
       </c>
       <c r="J4" s="2">
@@ -20572,54 +20876,54 @@
       <c r="Y4" s="2"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <f t="shared" ref="B5:L5" si="14">B7*B9</f>
         <v>1840.7103</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <f t="shared" si="14"/>
         <v>2005.5126</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <f t="shared" si="14"/>
         <v>2649.5828799999999</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <f t="shared" si="14"/>
         <v>2908.4988800000001</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <f t="shared" si="14"/>
         <v>3490.3444799999997</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <f t="shared" si="14"/>
         <v>6268.3129600000002</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <f t="shared" si="14"/>
         <v>6914.9184499999992</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <f t="shared" si="14"/>
         <v>7813.2380000000003</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <f t="shared" si="14"/>
         <v>8280.3240000000005</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="8">
         <f t="shared" si="14"/>
         <v>10610.054</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <f t="shared" si="14"/>
         <v>16194.324999999999</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="8">
         <f>M7*M9</f>
         <v>24726.096000000001</v>
       </c>
@@ -20655,8 +20959,8 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>527</v>
+      <c r="A6" s="9" t="s">
+        <v>522</v>
       </c>
       <c r="B6" s="2">
         <f t="shared" ref="B6:H6" si="15">B8*B9</f>
@@ -20748,8 +21052,8 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>528</v>
+      <c r="A7" s="13" t="s">
+        <v>523</v>
       </c>
       <c r="B7" s="2">
         <v>471.97699999999998</v>
@@ -20772,7 +21076,7 @@
       <c r="H7" s="2">
         <v>1075.415</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>1171.4000000000001</v>
       </c>
       <c r="J7" s="2">
@@ -20819,8 +21123,8 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>529</v>
+      <c r="A8" s="13" t="s">
+        <v>524</v>
       </c>
       <c r="B8" s="2">
         <v>123.057</v>
@@ -20874,10 +21178,10 @@
       <c r="S8" s="2">
         <v>3787.1</v>
       </c>
-      <c r="T8" s="13">
+      <c r="T8" s="12">
         <v>4779.7</v>
       </c>
-      <c r="U8" s="13">
+      <c r="U8" s="12">
         <v>4691</v>
       </c>
       <c r="V8" s="2">
@@ -20888,88 +21192,88 @@
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>523</v>
-      </c>
-      <c r="B9" s="15">
+      <c r="A9" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="B9" s="14">
         <v>3.9</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <v>3.9</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <v>3.92</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <v>3.92</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>3.92</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="14">
         <v>6.02</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="14">
         <v>6.43</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="14">
         <v>6.67</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="14">
         <v>6.76</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="14">
         <v>6.79</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="14">
         <v>7.25</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="14">
         <v>7.44</v>
       </c>
-      <c r="N9" s="12">
+      <c r="N9" s="11">
         <f t="shared" ref="N9:U9" si="19">N5/N7</f>
         <v>7.3790876579103095</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="11">
         <f t="shared" si="19"/>
         <v>7.5</v>
       </c>
-      <c r="P9" s="12">
+      <c r="P9" s="11">
         <f t="shared" si="19"/>
         <v>7.4109915816365799</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="Q9" s="11">
         <f t="shared" si="19"/>
         <v>7.5940838126540671</v>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="11">
         <f t="shared" si="19"/>
         <v>8.1311990233718436</v>
       </c>
-      <c r="S9" s="12">
+      <c r="S9" s="11">
         <f t="shared" si="19"/>
         <v>8.6380011577467535</v>
       </c>
-      <c r="T9" s="12">
+      <c r="T9" s="11">
         <f t="shared" si="19"/>
         <v>14.002003226673835</v>
       </c>
-      <c r="U9" s="12">
+      <c r="U9" s="11">
         <f t="shared" si="19"/>
         <v>19.859301751788799</v>
       </c>
-      <c r="V9" s="12">
+      <c r="V9" s="11">
         <f>V5/V7</f>
         <v>18.896310806398954</v>
       </c>
-      <c r="W9" s="12">
+      <c r="W9" s="11">
         <f t="shared" ref="W9" si="20">W5/W7</f>
         <v>20.519406611675937</v>
       </c>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="12"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21009,7 +21313,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>474</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -21017,21 +21321,21 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
+      <c r="A5" s="15"/>
       <c r="B5" s="4" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
+      <c r="A6" s="15"/>
       <c r="B6" s="4" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="4" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -21046,8 +21350,8 @@
       <c r="A9" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>503</v>
+      <c r="B9" s="16" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -21062,141 +21366,141 @@
       <c r="A12" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B12" t="s">
-        <v>506</v>
+      <c r="B12" s="17" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="B13" t="s">
-        <v>507</v>
+      <c r="B13" s="17" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B14" t="s">
-        <v>507</v>
+      <c r="B14" s="17" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>485</v>
       </c>
-      <c r="B15" t="s">
-        <v>508</v>
+      <c r="B15" s="17" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>486</v>
       </c>
-      <c r="B16" t="s">
-        <v>508</v>
+      <c r="B16" s="17" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="B17" t="s">
-        <v>491</v>
+      <c r="B17" s="17" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>485</v>
       </c>
-      <c r="B18" t="s">
-        <v>508</v>
+      <c r="B18" s="17" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>486</v>
       </c>
-      <c r="B19" t="s">
-        <v>508</v>
+      <c r="B19" s="17" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="B20" t="s">
-        <v>506</v>
+      <c r="B20" s="17" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B21" t="s">
-        <v>506</v>
+      <c r="B21" s="17" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B22" t="s">
-        <v>506</v>
+      <c r="B22" s="17" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>509</v>
+        <v>503</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>509</v>
+        <v>504</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>525</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>531</v>
+      <c r="A28" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>526</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>528</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>531</v>
+      <c r="A30" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>531</v>
+      <c r="A31" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>526</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Fiscal Data/ngdebt.xlsx
+++ b/Data/Fiscal Data/ngdebt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AJ\GitHub Repositories\PH-Econ-Data\Data\Fiscal Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0846D7-A126-4F88-9A0B-A9B961C73E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE19AC6-30B7-45FD-AF75-9134252E92A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1796,11 +1796,11 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4411,17 +4411,23 @@
         <v>18052386</v>
       </c>
       <c r="RN2" s="2">
-        <v>18479047</v>
+        <v>18479047.219999999</v>
       </c>
       <c r="RO2" s="2">
-        <v>18539680</v>
+        <v>18539680.300000001</v>
       </c>
       <c r="RP2" s="2">
-        <v>18869540</v>
-      </c>
-      <c r="RQ2" s="2"/>
-      <c r="RR2" s="2"/>
-      <c r="RS2" s="2"/>
+        <v>18869540.300000001</v>
+      </c>
+      <c r="RQ2" s="2">
+        <v>18853820.300000001</v>
+      </c>
+      <c r="RR2" s="2">
+        <v>18990213.300000001</v>
+      </c>
+      <c r="RS2" s="2">
+        <v>19370764.300000001</v>
+      </c>
       <c r="RT2" s="2"/>
       <c r="RU2" s="2"/>
       <c r="RV2" s="2"/>
@@ -5706,17 +5712,23 @@
         <v>17707814</v>
       </c>
       <c r="RN3" s="2">
-        <v>18133963</v>
+        <v>18133962.57</v>
       </c>
       <c r="RO3" s="2">
-        <v>18159698</v>
+        <v>18159698.300000001</v>
       </c>
       <c r="RP3" s="2">
-        <v>18488134</v>
-      </c>
-      <c r="RQ3" s="2"/>
-      <c r="RR3" s="2"/>
-      <c r="RS3" s="2"/>
+        <v>18488134.300000001</v>
+      </c>
+      <c r="RQ3" s="2">
+        <v>18470595.300000001</v>
+      </c>
+      <c r="RR3" s="2">
+        <v>18546711.300000001</v>
+      </c>
+      <c r="RS3" s="2">
+        <v>19065689.300000001</v>
+      </c>
       <c r="RT3" s="2"/>
       <c r="RU3" s="2"/>
       <c r="RV3" s="2"/>
@@ -7001,17 +7013,23 @@
         <v>12116253</v>
       </c>
       <c r="RN4" s="2">
-        <v>12324775</v>
+        <v>12324774.57</v>
       </c>
       <c r="RO4" s="2">
-        <v>12479162</v>
+        <v>12479162.300000001</v>
       </c>
       <c r="RP4" s="2">
-        <v>12534566</v>
-      </c>
-      <c r="RQ4" s="2"/>
-      <c r="RR4" s="2"/>
-      <c r="RS4" s="2"/>
+        <v>12534566.300000001</v>
+      </c>
+      <c r="RQ4" s="2">
+        <v>12415390.300000001</v>
+      </c>
+      <c r="RR4" s="2">
+        <v>12495513.300000001</v>
+      </c>
+      <c r="RS4" s="2">
+        <v>12837836.300000001</v>
+      </c>
       <c r="RT4" s="2"/>
       <c r="RU4" s="2"/>
       <c r="RV4" s="2"/>
@@ -8256,9 +8274,15 @@
       <c r="RP5" s="2">
         <v>156</v>
       </c>
-      <c r="RQ5" s="2"/>
-      <c r="RR5" s="2"/>
-      <c r="RS5" s="2"/>
+      <c r="RQ5" s="2">
+        <v>156</v>
+      </c>
+      <c r="RR5" s="2">
+        <v>156</v>
+      </c>
+      <c r="RS5" s="2">
+        <v>156</v>
+      </c>
       <c r="RT5" s="2"/>
       <c r="RU5" s="2"/>
       <c r="RV5" s="2"/>
@@ -9495,17 +9519,23 @@
         <v>12116097</v>
       </c>
       <c r="RN6" s="2">
-        <v>12324619</v>
+        <v>12324618.57</v>
       </c>
       <c r="RO6" s="2">
-        <v>12479006</v>
+        <v>12479006.300000001</v>
       </c>
       <c r="RP6" s="2">
-        <v>12534410</v>
-      </c>
-      <c r="RQ6" s="2"/>
-      <c r="RR6" s="2"/>
-      <c r="RS6" s="2"/>
+        <v>12534410.300000001</v>
+      </c>
+      <c r="RQ6" s="2">
+        <v>12415234.300000001</v>
+      </c>
+      <c r="RR6" s="2">
+        <v>12495357.300000001</v>
+      </c>
+      <c r="RS6" s="2">
+        <v>12837680.300000001</v>
+      </c>
       <c r="RT6" s="2"/>
       <c r="RU6" s="2"/>
       <c r="RV6" s="2"/>
@@ -10798,9 +10828,15 @@
       <c r="RP7" s="2">
         <v>5953568</v>
       </c>
-      <c r="RQ7" s="2"/>
-      <c r="RR7" s="2"/>
-      <c r="RS7" s="2"/>
+      <c r="RQ7" s="2">
+        <v>6055205</v>
+      </c>
+      <c r="RR7" s="2">
+        <v>6051198</v>
+      </c>
+      <c r="RS7" s="2">
+        <v>6227853</v>
+      </c>
       <c r="RT7" s="2"/>
       <c r="RU7" s="2"/>
       <c r="RV7" s="2"/>
@@ -12045,9 +12081,15 @@
       <c r="RP8" s="2">
         <v>2944109</v>
       </c>
-      <c r="RQ8" s="2"/>
-      <c r="RR8" s="2"/>
-      <c r="RS8" s="2"/>
+      <c r="RQ8" s="2">
+        <v>2998755</v>
+      </c>
+      <c r="RR8" s="2">
+        <v>2999465</v>
+      </c>
+      <c r="RS8" s="2">
+        <v>3039936</v>
+      </c>
       <c r="RT8" s="2"/>
       <c r="RU8" s="2"/>
       <c r="RV8" s="2"/>
@@ -13292,9 +13334,15 @@
       <c r="RP9" s="2">
         <v>3009459</v>
       </c>
-      <c r="RQ9" s="2"/>
-      <c r="RR9" s="2"/>
-      <c r="RS9" s="2"/>
+      <c r="RQ9" s="2">
+        <v>3056450</v>
+      </c>
+      <c r="RR9" s="2">
+        <v>3051733</v>
+      </c>
+      <c r="RS9" s="2">
+        <v>3187917</v>
+      </c>
       <c r="RT9" s="2"/>
       <c r="RU9" s="2"/>
       <c r="RV9" s="2"/>
@@ -14195,7 +14243,7 @@
         <v>344572</v>
       </c>
       <c r="RN10" s="2">
-        <v>345084</v>
+        <v>345084.65</v>
       </c>
       <c r="RO10" s="2">
         <v>379982</v>
@@ -14203,9 +14251,15 @@
       <c r="RP10" s="2">
         <v>381406</v>
       </c>
-      <c r="RQ10" s="2"/>
-      <c r="RR10" s="2"/>
-      <c r="RS10" s="2"/>
+      <c r="RQ10" s="2">
+        <v>383225</v>
+      </c>
+      <c r="RR10" s="2">
+        <v>443502</v>
+      </c>
+      <c r="RS10" s="2">
+        <v>305075</v>
+      </c>
       <c r="RT10" s="2"/>
       <c r="RU10" s="2"/>
       <c r="RV10" s="2"/>
@@ -15114,9 +15168,15 @@
       <c r="RP11" s="2">
         <v>293268</v>
       </c>
-      <c r="RQ11" s="2"/>
-      <c r="RR11" s="2"/>
-      <c r="RS11" s="2"/>
+      <c r="RQ11" s="2">
+        <v>293217</v>
+      </c>
+      <c r="RR11" s="2">
+        <v>354835</v>
+      </c>
+      <c r="RS11" s="2">
+        <v>218134</v>
+      </c>
       <c r="RT11" s="2"/>
       <c r="RU11" s="2"/>
       <c r="RV11" s="2"/>
@@ -16017,7 +16077,7 @@
         <v>87840</v>
       </c>
       <c r="RN12" s="2">
-        <v>88353</v>
+        <v>88353.650000000009</v>
       </c>
       <c r="RO12" s="2">
         <v>85952</v>
@@ -16025,9 +16085,15 @@
       <c r="RP12" s="2">
         <v>88138</v>
       </c>
-      <c r="RQ12" s="2"/>
-      <c r="RR12" s="2"/>
-      <c r="RS12" s="2"/>
+      <c r="RQ12" s="2">
+        <v>90008</v>
+      </c>
+      <c r="RR12" s="2">
+        <v>88667</v>
+      </c>
+      <c r="RS12" s="2">
+        <v>86941</v>
+      </c>
       <c r="RT12" s="2"/>
       <c r="RU12" s="2"/>
       <c r="RV12" s="2"/>
@@ -17488,9 +17554,15 @@
       <c r="RP13" s="2">
         <v>96383</v>
       </c>
-      <c r="RQ13" s="2"/>
-      <c r="RR13" s="2"/>
-      <c r="RS13" s="2"/>
+      <c r="RQ13" s="2">
+        <v>63525</v>
+      </c>
+      <c r="RR13" s="2">
+        <v>84603</v>
+      </c>
+      <c r="RS13" s="2">
+        <v>62431</v>
+      </c>
       <c r="RT13" s="2"/>
       <c r="RU13" s="2"/>
       <c r="RV13" s="2"/>
@@ -18943,7 +19015,7 @@
         <v>15008</v>
       </c>
       <c r="RN14" s="2">
-        <v>9852</v>
+        <v>9851.7800000000007</v>
       </c>
       <c r="RO14" s="2">
         <v>381713</v>
@@ -18951,9 +19023,15 @@
       <c r="RP14" s="2">
         <v>72709</v>
       </c>
-      <c r="RQ14" s="2"/>
-      <c r="RR14" s="2"/>
-      <c r="RS14" s="2"/>
+      <c r="RQ14" s="2">
+        <v>251360</v>
+      </c>
+      <c r="RR14" s="2">
+        <v>12580</v>
+      </c>
+      <c r="RS14" s="2">
+        <v>14788</v>
+      </c>
       <c r="RT14" s="2"/>
       <c r="RU14" s="2"/>
       <c r="RV14" s="2"/>
@@ -21313,7 +21391,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="17" t="s">
         <v>474</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -21321,19 +21399,19 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="4" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
+      <c r="A6" s="17"/>
       <c r="B6" s="4" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="4" t="s">
         <v>517</v>
       </c>
@@ -21350,7 +21428,7 @@
       <c r="A9" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>529</v>
       </c>
     </row>
@@ -21366,7 +21444,7 @@
       <c r="A12" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>539</v>
       </c>
     </row>
@@ -21374,7 +21452,7 @@
       <c r="A13" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>540</v>
       </c>
     </row>
@@ -21382,7 +21460,7 @@
       <c r="A14" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>540</v>
       </c>
     </row>
@@ -21390,7 +21468,7 @@
       <c r="A15" t="s">
         <v>485</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>541</v>
       </c>
     </row>
@@ -21398,7 +21476,7 @@
       <c r="A16" t="s">
         <v>486</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>541</v>
       </c>
     </row>
@@ -21406,7 +21484,7 @@
       <c r="A17" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>540</v>
       </c>
     </row>
@@ -21414,7 +21492,7 @@
       <c r="A18" t="s">
         <v>485</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>541</v>
       </c>
     </row>
@@ -21422,7 +21500,7 @@
       <c r="A19" t="s">
         <v>486</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>541</v>
       </c>
     </row>
@@ -21430,7 +21508,7 @@
       <c r="A20" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>539</v>
       </c>
     </row>
@@ -21438,7 +21516,7 @@
       <c r="A21" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>539</v>
       </c>
     </row>
@@ -21446,7 +21524,7 @@
       <c r="A22" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>539</v>
       </c>
     </row>
@@ -21454,7 +21532,7 @@
       <c r="A23" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>542</v>
       </c>
     </row>
@@ -21462,7 +21540,7 @@
       <c r="A24" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="16" t="s">
         <v>542</v>
       </c>
     </row>
